--- a/samples/ExcelFormulaLabs-Samples.xlsx
+++ b/samples/ExcelFormulaLabs-Samples.xlsx
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -765,7 +765,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,6 +873,28 @@
       </c>
       <c r="C10" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>模型质量（交叉验证 R²/MAE）</t>
+        </is>
+      </c>
+      <c r="G13">
+        <f>SOLVE.QUALITY(A4:C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>前向方程 + 闭式反解式</t>
+        </is>
+      </c>
+      <c r="G14">
+        <f>SOLVE.EQUATION(A4:C11)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -948,25 +970,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DOE.* — 实验设计（全因子 2 因子 × 2 水平）</t>
+          <t>DOE.* — 实验设计 + 效应分析（2 因子全因子，coded ±1）</t>
         </is>
       </c>
     </row>
     <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>设计矩阵（含 StdOrder/RunOrder）</t>
@@ -974,6 +1012,83 @@
       </c>
       <c r="G3">
         <f>DOE.PLAN(2,2,0,2,"full",FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>效应分析（ANALYZE）</t>
+        </is>
+      </c>
+      <c r="G12">
+        <f>DOE.ANALYZE(A4:B7, C4:C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ANOVA 表</t>
+        </is>
+      </c>
+      <c r="G13">
+        <f>DOE.ANOVA(A4:B7, C4:C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Pareto 效应排序</t>
+        </is>
+      </c>
+      <c r="G14">
+        <f>DOE.PARETO(A4:B7, C4:C7)</f>
         <v/>
       </c>
     </row>

--- a/samples/ExcelFormulaLabs-Samples.xlsx
+++ b/samples/ExcelFormulaLabs-Samples.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -616,13 +616,13 @@
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="F8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>解方程组 Ax=b</t>
         </is>
       </c>
-      <c r="G8">
+      <c r="G9">
         <f>LINALG.SOLVE(A4:C6, E4:E6)</f>
         <v/>
       </c>
@@ -692,15 +692,6 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>OLS 报告（11 行）</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>REGRESS.OLS(A4:A8, B4:C8)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -711,6 +702,15 @@
       </c>
       <c r="C5" t="n">
         <v>1</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>OLS 报告（11 行 × 2 列）</t>
+        </is>
+      </c>
+      <c r="G5">
+        <f>REGRESS.OLS(A4:A8, B4:C8)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -886,13 +886,13 @@
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="F14" s="3" t="inlineStr">
+    <row r="19">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>前向方程 + 闭式反解式</t>
         </is>
       </c>
-      <c r="G14">
+      <c r="G19">
         <f>SOLVE.EQUATION(A4:C11)</f>
         <v/>
       </c>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -937,24 +937,24 @@
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>分子量 H2SO4</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>PHYCHEM.MOLWT("H2SO4")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5">
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>分子量 H2SO4</t>
+        </is>
+      </c>
+      <c r="G5">
+        <f>PHYCHEM.MOLWT("H2SO4")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>密度 = 质量/体积</t>
         </is>
       </c>
-      <c r="G5">
+      <c r="G7">
         <f>PHYCHEM.DENSITY(100, 2)</f>
         <v/>
       </c>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1070,24 +1070,24 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" s="3" t="inlineStr">
+    <row r="16">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>ANOVA 表</t>
         </is>
       </c>
-      <c r="G13">
+      <c r="G16">
         <f>DOE.ANOVA(A4:B7, C4:C7)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="F14" s="3" t="inlineStr">
+    <row r="22">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Pareto 效应排序</t>
         </is>
       </c>
-      <c r="G14">
+      <c r="G22">
         <f>DOE.PARETO(A4:B7, C4:C7)</f>
         <v/>
       </c>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="G3">
-        <f>PIVOT.GROUPBY(A4:C8, {1}, 3, "sum")</f>
+        <f>PIVOT.GROUPBY(A4:C8, {0}, 2, "sum")</f>
         <v/>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1432,24 +1432,24 @@
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>取扩展名</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>FS.EXT("C:\data\report.xlsx")</f>
-        <v/>
-      </c>
-    </row>
     <row r="5">
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>取扩展名</t>
+        </is>
+      </c>
+      <c r="G5">
+        <f>FS.EXT("C:\data\report.xlsx")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>规范化路径</t>
         </is>
       </c>
-      <c r="G5">
+      <c r="G7">
         <f>FS.NORM("C:\data\..\file.txt")</f>
         <v/>
       </c>
@@ -1504,15 +1504,6 @@
       <c r="A4" t="n">
         <v>12.5</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>样本标准差</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>STATS.STDEV(A4:A13)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1520,11 +1511,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>中位数</t>
+          <t>样本标准差</t>
         </is>
       </c>
       <c r="G5">
-        <f>STATS.MEDIAN(A4:A13)</f>
+        <f>STATS.STDEV(A4:A13)</f>
         <v/>
       </c>
     </row>
@@ -1532,20 +1523,20 @@
       <c r="A6" t="n">
         <v>11.8</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>描述统计摘要（9 值溢出）</t>
-        </is>
-      </c>
-      <c r="G6">
-        <f>STATS.SUMMARY(A4:A13)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>14.2</v>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>中位数</t>
+        </is>
+      </c>
+      <c r="G7">
+        <f>STATS.MEDIAN(A4:A13)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1555,6 +1546,15 @@
     <row r="9">
       <c r="A9" t="n">
         <v>12.9</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>描述统计摘要（9 值溢出）</t>
+        </is>
+      </c>
+      <c r="G9">
+        <f>STATS.SUMMARY(A4:A13)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1628,15 +1628,6 @@
           <t>hello world</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>首字母大写</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>STR.TITLE(A4)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1646,11 +1637,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>连接数组（忽略空）</t>
+          <t>首字母大写</t>
         </is>
       </c>
       <c r="G5">
-        <f>STR.TEXTJOIN("-", TRUE, A4:A6)</f>
+        <f>STR.TITLE(A4)</f>
         <v/>
       </c>
     </row>
@@ -1659,6 +1650,17 @@
         <is>
           <t xml:space="preserve">  spaced  </t>
         </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>连接数组（忽略空）</t>
+        </is>
+      </c>
+      <c r="G7">
+        <f>STR.TEXTJOIN("-", TRUE, A4:A6)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1672,7 +1674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1712,15 +1714,6 @@
           <t>Order A-1024 x3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>是否含数字</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>REGEX.ISMATCH(A4, "\d+")</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1730,11 +1723,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>替换全部数字为 #</t>
+          <t>是否含数字</t>
         </is>
       </c>
       <c r="G5">
-        <f>REGEX.REPLACE(A4, "\d", "#")</f>
+        <f>REGEX.ISMATCH(A4, "\d+")</f>
         <v/>
       </c>
     </row>
@@ -1743,6 +1736,17 @@
         <is>
           <t>tel 138-0000-0000</t>
         </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>替换全部数字为 #</t>
+        </is>
+      </c>
+      <c r="G7">
+        <f>REGEX.REPLACE(A4, "\d", "#")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1756,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1785,24 +1789,24 @@
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2024 是否闰年</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>DT.ISLEAP(2024)</f>
-        <v/>
-      </c>
-    </row>
     <row r="5">
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>2024 是否闰年</t>
+        </is>
+      </c>
+      <c r="G5">
+        <f>DT.ISLEAP(2024)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>2026 复活节日期</t>
         </is>
       </c>
-      <c r="G5">
+      <c r="G7">
         <f>DT.EASTER(2026)</f>
         <v/>
       </c>
@@ -1818,7 +1822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1856,29 +1860,11 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>降序排列</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>ARR.SORTDESC(A4:A10)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>切片（从索引 1 起 3 个）</t>
-        </is>
-      </c>
-      <c r="G5">
-        <f>ARR.SLICE(A4:A10, 1, 3)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1903,6 +1889,28 @@
     <row r="10">
       <c r="A10" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>降序排列</t>
+        </is>
+      </c>
+      <c r="G11">
+        <f>ARR.SORTDESC(A4:A10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>切片（从索引 1 起 3 个）</t>
+        </is>
+      </c>
+      <c r="G19">
+        <f>ARR.SLICE(A4:A10, 1, 3)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1916,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1956,15 +1964,6 @@
           <t>{"name":"Alice","scores":[90,85]}</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>取数组元素</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>JSON.QUERY(A4, "scores[0]")</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1974,21 +1973,32 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>取数组元素</t>
+        </is>
+      </c>
+      <c r="G5">
+        <f>JSON.QUERY(A4, "scores[0]")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>是否合法 JSON</t>
         </is>
       </c>
-      <c r="G5">
+      <c r="G7">
         <f>JSON.VALIDATE(A4)</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="F6" s="3" t="inlineStr">
+    <row r="9">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>美化输出</t>
         </is>
       </c>
-      <c r="G6">
+      <c r="G9">
         <f>JSON.PRETTIFY(A4)</f>
         <v/>
       </c>
@@ -2004,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2044,12 +2054,14 @@
           <t>&lt;r&gt;&lt;n&gt;1&lt;/n&gt;&lt;n&gt;2&lt;/n&gt;&lt;n&gt;3&lt;/n&gt;&lt;/r&gt;</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>XPath 查询（溢出）</t>
         </is>
       </c>
-      <c r="G4">
+      <c r="G5">
         <f>XML.XPATH(A4, "//n")</f>
         <v/>
       </c>
